--- a/plan_kotlin_4.xlsx
+++ b/plan_kotlin_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxis\Desktop\kotlin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EDEBC7-FCCF-48BE-8B1F-7CF3B0291207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD44863-3107-4688-9D75-99E1E1856D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="22905" yWindow="6375" windowWidth="2400" windowHeight="585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="План Kotlin 4" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="174">
   <si>
     <t>Дата</t>
   </si>
@@ -549,6 +549,9 @@
   </si>
   <si>
     <t>Docker: образ vs контейнер, зачем docker-compose</t>
+  </si>
+  <si>
+    <t>Да</t>
   </si>
 </sst>
 </file>
@@ -1018,7 +1021,9 @@
       <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -1105,11 +1110,15 @@
       <c r="D6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>36</v>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наследование и интерфейсы: Kotlin + Java</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">День 04: общая «Фигура» и три наследника — круг, прямоугольник, треугольник (площадь по формуле Герона; треугольник с невозможными сторонами не должен создаваться). Функция, которая складывает площади любых фигур, не зная, какие они. Сотрудник и Менеджер: у менеджера зарплата = зарплата сотрудника + бонус, через вызов родителя. Интерфейс «Логгер» с готовым методом «залогировать ошибку», который дописывает ERROR: к сообщению. И случай, когда класс реализует два интерфейса с одинаковым методом — разрули конфликт явно. Вместо часа Kotlin Koans: 45–60 минут Java. Разбери объявление класса, конструктор, public/private, extends и implements. Перепиши Сотрудника и Менеджера на Java, проверь расчёт зарплаты. Сравни с Kotlin. Практику Java делай в том же проекте, в src/main/java; новый проект и установки не нужны.</t>
+        </is>
       </c>
       <c r="G6" s="3" t="s">
         <v>37</v>
@@ -1155,11 +1164,15 @@
       <c r="D8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>46</v>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data class, enum и равенство Kotlin/Java</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дальше без тестов, пишешь в своём файле. 1) Опиши «Товар» (название, цена, категория) как data class. Создай два одинаковых товара и проверь: они равны по содержимому (==), но это разные объекты (===). Сделай копию товара с другой ценой через copy. 2) Категория — перечисление (еда, книги, прочее), у каждой своя ставка НДС. Напиши функцию «цена с НДС»: хлеб за 100 в категории «еда» со ставкой 10% → 110. 3) Вместо задачи со сторонами света: 30 минут Java. Создай обычный класс «Товар» с конструктором и геттерами, сравни два экземпляра через == и equals. Сгенерируй equals и hashCode в IDE и повтори проверку. Объясни отличие от data class.</t>
+        </is>
       </c>
       <c r="G8" s="3" t="s">
         <v>47</v>
@@ -1180,11 +1193,15 @@
       <c r="D9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>50</v>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лямбды Kotlin + основы Java</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1) Функция, которая принимает число и другую функцию и применяет её дважды: число 3 и «умножить на 2» → 12. 2) Функция, которая из двух функций делает одну («сначала прибавить 1, потом умножить на 2»: 5 → 12). 3) «Фабрика счётчика»: возвращает функцию, которая при каждом вызове выдаёт следующее число — 1, 2, 3… (это замыкание). 4) Свой фильтр списка через цикл, принимающий условие как параметр. 5) Вместо повторного переписывания трёх задач: 30–40 минут Java. Самостоятельно перепиши сумму цифр и максимум списка из дня 01 на Java; проверь ноль, отрицательное число и пустой список. Разбери int/long, Integer/Long, null, static, return и throw. В заметки: что такое тип функции, что такое it, зачем лямбду выносят за скобки.</t>
+        </is>
       </c>
       <c r="G9" s="3" t="s">
         <v>51</v>
@@ -1301,11 +1318,15 @@
       <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>67</v>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дженерики Kotlin/Java + повторение</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1) «Коробка», в которую можно положить значение любого типа, с методом «преобразовать содержимое»: коробка с 3 → «умножить на 2» → коробка с 6. 2) Стек для любого типа (переделай стек чисел из дня 03). 3) Функция «максимум из списка» для любого типа, который умеет сравниваться. 4) Вместо переворота словаря: 30–40 минут Java. Сделай простую коробку для любого типа и проверь её со строкой и числом. Сравни тип-параметр с Kotlin. Пойми, почему в коллекциях пишут Integer, а не int. Потом 1,5 часа: перечитай все заметки за две недели и перепиши 2–3 задачи, где ошибался.</t>
+        </is>
       </c>
       <c r="G14" s="3" t="s">
         <v>68</v>
@@ -1351,11 +1372,15 @@
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>76</v>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Коллекции, equals/hashCode: Kotlin + Java</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1) Положи в множество (HashSet) два объекта обычного класса с одинаковыми полями — почему их два? Переопредели equals и hashCode — станет один. 2) Своими словами в заметки: когда брать список, когда множество, когда словарь. 3) Один и тот же набор операций map/filter на обычном списке и на asSequence() — объясни разницу (ленивые вычисления). 4) Вместо трёх задач 6 kyu: одна задача на коллекции на Kotlin и 45–60 минут Java. Посчитай частоты слов через HashMap, убери повторы через HashSet и сравни ArrayList с LinkedList. Проверь два равных товара в HashSet, используя equals и hashCode.</t>
+        </is>
       </c>
       <c r="G16" s="3" t="s">
         <v>77</v>
@@ -1373,14 +1398,20 @@
       <c r="C17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>80</v>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,5–2ч</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Java Core: классы, исключения, Stream API</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Java-практика в том же проекте. 1) Перепиши Прямоугольник и Счётчик на Java: конструктор, private-поле, геттер, методы изменения; проверь невозможность изменить поле напрямую. 2) В конструкторе Прямоугольника брось исключение при недопустимой стороне, поймай его при вызове. Сравни checked и unchecked исключения, throws, try/catch. 3) Из списка товаров выбери дорогие и получи названия сначала циклом, затем через Stream API. 4) Коротко запиши отличия: == и equals, final и val, null, static, data class и обычный класс. Если времени не хватило — отметь «Частично», не добавляй часы сверх плана.</t>
+        </is>
       </c>
       <c r="G17" s="3" t="s">
         <v>81</v>
@@ -1497,11 +1528,15 @@
       <c r="D22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>97</v>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JDBC: Kotlin и чтение Java-кода</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подключись из Kotlin к своей базе через JDBC. Напиши «заказы клиента по имени» и «добавить заказ», используя PreparedStatement с параметрами и закрытие ресурсов через use. Проверь запись и чтение. Последние 20 минут в рамках занятия: перепиши только чтение заказов на Java с try-with-resources. Сравни закрытие соединения и обработку SQLException. Если не успел, Java-вариант перенеси в повторение, SQL-практику не сокращай.</t>
+        </is>
       </c>
       <c r="G22" s="3" t="s">
         <v>98</v>
@@ -1738,8 +1773,10 @@
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>128</v>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Читать без кода запрещено: минимум 60% времени дня — в IDE. Чтение 29.09–02.10 без кода — именно так теряется неделя. Java-блоки заменяют часть повторения, а не увеличивают часы. Дни отдыха не занимать. После подсказки переписать решение самостоятельно. Java-файлы — в src/main/java существующего Gradle-проекта; Kotlin-задания и тесты сохраняются.</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -1792,8 +1829,10 @@
       </c>
     </row>
     <row r="21" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>137</v>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Java/Kotlin JVM backend: после 01.11 — Spring Boot (REST, слои, Spring Data JPA, валидация, тесты), практика Java Core и основы Maven, затем законченный pet-проект. Java — полноценная часть подготовки к Java-вакансиям, не только чтение кода. Не делать два больших проекта одновременно. Отдельный следующий план уточнить по результатам чекпоинта.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1803,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2130,6 +2169,108 @@
         <v>82</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>int и Integer, long и Long: чем отличаются, где возможен null, что такое boxing/unboxing</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>13.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>== и equals в Java против Kotlin; почему equals и hashCode нужны вместе</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>20.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>private/public, конструктор, extends/implements, static и final — объяснить на своих классах</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>21.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>ArrayList, LinkedList, HashSet, HashMap — когда что выбрать</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>20.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Лямбда, функциональный интерфейс и Stream API: filter/map, отличие от Kotlin Sequence</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>21.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>checked/unchecked исключения, throw/throws, try-with-resources — зачем</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>26.10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
